--- a/output/dataverse/Supplementary_Table_1_EAR.xlsx
+++ b/output/dataverse/Supplementary_Table_1_EAR.xlsx
@@ -391,13 +391,13 @@
         <v>7575436</v>
       </c>
       <c r="C2">
-        <v>247.55</v>
+        <v>244.97</v>
       </c>
       <c r="D2">
-        <v>3.73</v>
+        <v>3.93</v>
       </c>
       <c r="E2">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -410,13 +410,13 @@
         <v>2307038</v>
       </c>
       <c r="C3">
-        <v>277.5</v>
+        <v>274.74</v>
       </c>
       <c r="D3">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="E3">
-        <v>3.44</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="4">
@@ -429,13 +429,13 @@
         <v>912942</v>
       </c>
       <c r="C4">
-        <v>273.19</v>
+        <v>269.5</v>
       </c>
       <c r="D4">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="E4">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="5">
@@ -448,13 +448,13 @@
         <v>624656</v>
       </c>
       <c r="C5">
-        <v>278.73</v>
+        <v>275.43</v>
       </c>
       <c r="D5">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="E5">
-        <v>5.76</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="6">
@@ -467,13 +467,13 @@
         <v>460509</v>
       </c>
       <c r="C6">
-        <v>271.55</v>
+        <v>269.18</v>
       </c>
       <c r="D6">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="E6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
@@ -486,13 +486,13 @@
         <v>369802</v>
       </c>
       <c r="C7">
-        <v>258.9</v>
+        <v>255.65</v>
       </c>
       <c r="D7">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="E7">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="8">
@@ -505,13 +505,13 @@
         <v>1828298</v>
       </c>
       <c r="C8">
-        <v>187.01</v>
+        <v>185.42</v>
       </c>
       <c r="D8">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="E8">
-        <v>5.28</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="9">
@@ -524,13 +524,13 @@
         <v>1072189</v>
       </c>
       <c r="C9">
-        <v>232.11</v>
+        <v>229.73</v>
       </c>
       <c r="D9">
-        <v>10.19</v>
+        <v>10.38</v>
       </c>
       <c r="E9">
-        <v>11.35</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="10">
@@ -543,13 +543,13 @@
         <v>35957</v>
       </c>
       <c r="C10">
-        <v>247.44</v>
+        <v>244.59</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E10">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="11">
@@ -562,13 +562,13 @@
         <v>2861</v>
       </c>
       <c r="C11">
-        <v>240.19</v>
+        <v>237.53</v>
       </c>
       <c r="D11">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
       <c r="E11">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="12">
@@ -581,13 +581,13 @@
         <v>41899</v>
       </c>
       <c r="C12">
-        <v>287.56</v>
+        <v>284.79</v>
       </c>
       <c r="D12">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="E12">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="13">
@@ -600,13 +600,13 @@
         <v>30630</v>
       </c>
       <c r="C13">
-        <v>165.28</v>
+        <v>163.43</v>
       </c>
       <c r="D13">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="E13">
-        <v>7.04</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="14">
@@ -619,13 +619,13 @@
         <v>90</v>
       </c>
       <c r="C14">
-        <v>247.38</v>
+        <v>244.78</v>
       </c>
       <c r="D14">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="E14">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="15">
@@ -638,13 +638,13 @@
         <v>44152</v>
       </c>
       <c r="C15">
-        <v>279.91</v>
+        <v>275.97</v>
       </c>
       <c r="D15">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="E15">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="16">
@@ -657,13 +657,13 @@
         <v>2871</v>
       </c>
       <c r="C16">
-        <v>367.79</v>
+        <v>363.95</v>
       </c>
       <c r="D16">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E16">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17">
@@ -676,13 +676,13 @@
         <v>25005</v>
       </c>
       <c r="C17">
-        <v>242.05</v>
+        <v>238.88</v>
       </c>
       <c r="D17">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="E17">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="18">
@@ -695,13 +695,13 @@
         <v>8776</v>
       </c>
       <c r="C18">
-        <v>223.24</v>
+        <v>219.73</v>
       </c>
       <c r="D18">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
       <c r="E18">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="19">
@@ -714,7 +714,7 @@
         <v>9939</v>
       </c>
       <c r="C19">
-        <v>382.96</v>
+        <v>379.89</v>
       </c>
       <c r="D19">
         <v>0.01</v>
@@ -733,13 +733,13 @@
         <v>389</v>
       </c>
       <c r="C20">
-        <v>188.82</v>
+        <v>186.52</v>
       </c>
       <c r="D20">
-        <v>16.27</v>
+        <v>16.75</v>
       </c>
       <c r="E20">
-        <v>16.27</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="21">
@@ -752,13 +752,13 @@
         <v>1472</v>
       </c>
       <c r="C21">
-        <v>296.09</v>
+        <v>294.47</v>
       </c>
       <c r="D21">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="E21">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22">
@@ -771,13 +771,13 @@
         <v>160973</v>
       </c>
       <c r="C22">
-        <v>196.11</v>
+        <v>194.46</v>
       </c>
       <c r="D22">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="E22">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="23">
@@ -790,13 +790,13 @@
         <v>278</v>
       </c>
       <c r="C23">
-        <v>183</v>
+        <v>180.56</v>
       </c>
       <c r="D23">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="E23">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +809,13 @@
         <v>9376</v>
       </c>
       <c r="C24">
-        <v>240.62</v>
+        <v>237.72</v>
       </c>
       <c r="D24">
-        <v>7.83</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E24">
-        <v>7.83</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -828,7 +828,7 @@
         <v>11339</v>
       </c>
       <c r="C25">
-        <v>321.87</v>
+        <v>317.04</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -847,13 +847,13 @@
         <v>375</v>
       </c>
       <c r="C26">
-        <v>231.89</v>
+        <v>229.16</v>
       </c>
       <c r="D26">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="E26">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="27">
@@ -866,13 +866,13 @@
         <v>12119</v>
       </c>
       <c r="C27">
-        <v>219.13</v>
+        <v>216.72</v>
       </c>
       <c r="D27">
-        <v>17.85</v>
+        <v>18.11</v>
       </c>
       <c r="E27">
-        <v>18.51</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="28">
@@ -885,13 +885,13 @@
         <v>753</v>
       </c>
       <c r="C28">
-        <v>218.99</v>
+        <v>217.29</v>
       </c>
       <c r="D28">
-        <v>17.25</v>
+        <v>17.5</v>
       </c>
       <c r="E28">
-        <v>22.59</v>
+        <v>22.88</v>
       </c>
     </row>
     <row r="29">
@@ -904,13 +904,13 @@
         <v>11338</v>
       </c>
       <c r="C29">
-        <v>188.22</v>
+        <v>185.87</v>
       </c>
       <c r="D29">
-        <v>26.1</v>
+        <v>26.39</v>
       </c>
       <c r="E29">
-        <v>26.1</v>
+        <v>26.39</v>
       </c>
     </row>
     <row r="30">
@@ -923,13 +923,13 @@
         <v>3338</v>
       </c>
       <c r="C30">
-        <v>263.19</v>
+        <v>259.55</v>
       </c>
       <c r="D30">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="E30">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31">
@@ -942,13 +942,13 @@
         <v>2258</v>
       </c>
       <c r="C31">
-        <v>325.41</v>
+        <v>322.56</v>
       </c>
       <c r="D31">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="E31">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="32">
@@ -961,13 +961,13 @@
         <v>203931</v>
       </c>
       <c r="C32">
-        <v>356.4</v>
+        <v>352.42</v>
       </c>
       <c r="D32">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E32">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="33">
@@ -980,13 +980,13 @@
         <v>434</v>
       </c>
       <c r="C33">
-        <v>257.07</v>
+        <v>255.18</v>
       </c>
       <c r="D33">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="E33">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="34">
@@ -999,13 +999,13 @@
         <v>6938</v>
       </c>
       <c r="C34">
-        <v>178.07</v>
+        <v>175.53</v>
       </c>
       <c r="D34">
-        <v>3.26</v>
+        <v>4.62</v>
       </c>
       <c r="E34">
-        <v>3.26</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="35">
@@ -1018,7 +1018,7 @@
         <v>20003</v>
       </c>
       <c r="C35">
-        <v>378.27</v>
+        <v>374.27</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1037,13 +1037,13 @@
         <v>11642</v>
       </c>
       <c r="C36">
-        <v>201.17</v>
+        <v>198.99</v>
       </c>
       <c r="D36">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="E36">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="37">
@@ -1056,13 +1056,13 @@
         <v>16004</v>
       </c>
       <c r="C37">
-        <v>289.91</v>
+        <v>287.41</v>
       </c>
       <c r="D37">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="E37">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="38">
@@ -1075,7 +1075,7 @@
         <v>24278</v>
       </c>
       <c r="C38">
-        <v>304.16</v>
+        <v>300.85</v>
       </c>
       <c r="D38">
         <v>0.05</v>
@@ -1094,13 +1094,13 @@
         <v>37171</v>
       </c>
       <c r="C39">
-        <v>283.97</v>
+        <v>280.22</v>
       </c>
       <c r="D39">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="E39">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="40">
@@ -1113,10 +1113,10 @@
         <v>504</v>
       </c>
       <c r="C40">
-        <v>280.02</v>
+        <v>277.51</v>
       </c>
       <c r="D40">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="E40">
         <v>0.06</v>
@@ -1132,7 +1132,7 @@
         <v>4728</v>
       </c>
       <c r="C41">
-        <v>317.71</v>
+        <v>314.2</v>
       </c>
       <c r="D41">
         <v>0.01</v>
@@ -1151,13 +1151,13 @@
         <v>15756</v>
       </c>
       <c r="C42">
-        <v>210.88</v>
+        <v>208.46</v>
       </c>
       <c r="D42">
-        <v>19.33</v>
+        <v>19.63</v>
       </c>
       <c r="E42">
-        <v>19.33</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="43">
@@ -1170,13 +1170,13 @@
         <v>18840</v>
       </c>
       <c r="C43">
-        <v>266.64</v>
+        <v>263.11</v>
       </c>
       <c r="D43">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E43">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="44">
@@ -1189,13 +1189,13 @@
         <v>1406343</v>
       </c>
       <c r="C44">
-        <v>276.28</v>
+        <v>273.59</v>
       </c>
       <c r="D44">
-        <v>4.01</v>
+        <v>4.23</v>
       </c>
       <c r="E44">
-        <v>4.01</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="45">
@@ -1208,13 +1208,13 @@
         <v>48792</v>
       </c>
       <c r="C45">
-        <v>171.4</v>
+        <v>169.63</v>
       </c>
       <c r="D45">
-        <v>4.74</v>
+        <v>5.21</v>
       </c>
       <c r="E45">
-        <v>4.74</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="46">
@@ -1227,13 +1227,13 @@
         <v>756</v>
       </c>
       <c r="C46">
-        <v>234.94</v>
+        <v>232.46</v>
       </c>
       <c r="D46">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="E46">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="47">
@@ -1246,13 +1246,13 @@
         <v>5376</v>
       </c>
       <c r="C47">
-        <v>295.59</v>
+        <v>292.62</v>
       </c>
       <c r="D47">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="E47">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="48">
@@ -1265,13 +1265,13 @@
         <v>87795</v>
       </c>
       <c r="C48">
-        <v>127.47</v>
+        <v>126</v>
       </c>
       <c r="D48">
-        <v>21.24</v>
+        <v>21.88</v>
       </c>
       <c r="E48">
-        <v>21.24</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="49">
@@ -1284,13 +1284,13 @@
         <v>4913</v>
       </c>
       <c r="C49">
-        <v>233.68</v>
+        <v>230.87</v>
       </c>
       <c r="D49">
-        <v>0.97</v>
+        <v>1.12</v>
       </c>
       <c r="E49">
-        <v>0.97</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="50">
@@ -1303,13 +1303,13 @@
         <v>3968</v>
       </c>
       <c r="C50">
-        <v>268.74</v>
+        <v>264.72</v>
       </c>
       <c r="D50">
-        <v>0.36</v>
+        <v>0.57</v>
       </c>
       <c r="E50">
-        <v>0.36</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="51">
@@ -1322,13 +1322,13 @@
         <v>11104</v>
       </c>
       <c r="C51">
-        <v>314.64</v>
+        <v>310.17</v>
       </c>
       <c r="D51">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="E51">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="52">
@@ -1341,13 +1341,13 @@
         <v>1265</v>
       </c>
       <c r="C52">
-        <v>217.93</v>
+        <v>215.56</v>
       </c>
       <c r="D52">
-        <v>0.41</v>
+        <v>0.58</v>
       </c>
       <c r="E52">
-        <v>0.41</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="53">
@@ -1360,13 +1360,13 @@
         <v>10439</v>
       </c>
       <c r="C53">
-        <v>156.76</v>
+        <v>154.74</v>
       </c>
       <c r="D53">
-        <v>9.94</v>
+        <v>12</v>
       </c>
       <c r="E53">
-        <v>9.94</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54">
@@ -1379,13 +1379,13 @@
         <v>26907</v>
       </c>
       <c r="C54">
-        <v>286.93</v>
+        <v>283.86</v>
       </c>
       <c r="D54">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E54">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="55">
@@ -1398,13 +1398,13 @@
         <v>5745</v>
       </c>
       <c r="C55">
-        <v>295.48</v>
+        <v>291.19</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="56">
@@ -1417,13 +1417,13 @@
         <v>1057</v>
       </c>
       <c r="C56">
-        <v>343.6</v>
+        <v>340.76</v>
       </c>
       <c r="D56">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E56">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="57">
@@ -1436,13 +1436,13 @@
         <v>67</v>
       </c>
       <c r="C57">
-        <v>189.59</v>
+        <v>187.11</v>
       </c>
       <c r="D57">
-        <v>2.28</v>
+        <v>2.72</v>
       </c>
       <c r="E57">
-        <v>2.28</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="58">
@@ -1455,13 +1455,13 @@
         <v>10631</v>
       </c>
       <c r="C58">
-        <v>257.49</v>
+        <v>254.41</v>
       </c>
       <c r="D58">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E58">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -1474,13 +1474,13 @@
         <v>16910</v>
       </c>
       <c r="C59">
-        <v>83.54000000000001</v>
+        <v>82.59</v>
       </c>
       <c r="D59">
-        <v>80.04000000000001</v>
+        <v>80.13</v>
       </c>
       <c r="E59">
-        <v>80.04000000000001</v>
+        <v>80.13</v>
       </c>
     </row>
     <row r="60">
@@ -1493,13 +1493,13 @@
         <v>104191</v>
       </c>
       <c r="C60">
-        <v>257.74</v>
+        <v>255.37</v>
       </c>
       <c r="D60">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E60">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="61">
@@ -1512,13 +1512,13 @@
         <v>6120</v>
       </c>
       <c r="C61">
-        <v>272.94</v>
+        <v>269.64</v>
       </c>
       <c r="D61">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="E61">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="62">
@@ -1531,13 +1531,13 @@
         <v>1593</v>
       </c>
       <c r="C62">
-        <v>226.52</v>
+        <v>224.27</v>
       </c>
       <c r="D62">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="E62">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="63">
@@ -1550,13 +1550,13 @@
         <v>3128</v>
       </c>
       <c r="C63">
-        <v>270</v>
+        <v>267.37</v>
       </c>
       <c r="D63">
         <v>0.07000000000000001</v>
       </c>
       <c r="E63">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="64">
@@ -1569,13 +1569,13 @@
         <v>1310</v>
       </c>
       <c r="C64">
-        <v>233.13</v>
+        <v>229.56</v>
       </c>
       <c r="D64">
-        <v>1.1</v>
+        <v>1.58</v>
       </c>
       <c r="E64">
-        <v>1.1</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="65">
@@ -1588,13 +1588,13 @@
         <v>1145</v>
       </c>
       <c r="C65">
-        <v>136.53</v>
+        <v>135.3</v>
       </c>
       <c r="D65">
-        <v>14.89</v>
+        <v>15.18</v>
       </c>
       <c r="E65">
-        <v>30.06</v>
+        <v>30.54</v>
       </c>
     </row>
     <row r="66">
@@ -1607,13 +1607,13 @@
         <v>110537</v>
       </c>
       <c r="C66">
-        <v>298.44</v>
+        <v>295.67</v>
       </c>
       <c r="D66">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E66">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="67">
@@ -1626,13 +1626,13 @@
         <v>899</v>
       </c>
       <c r="C67">
-        <v>193.24</v>
+        <v>191.48</v>
       </c>
       <c r="D67">
-        <v>23.03</v>
+        <v>23.3</v>
       </c>
       <c r="E67">
-        <v>24.51</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="68">
@@ -1645,13 +1645,13 @@
         <v>5471</v>
       </c>
       <c r="C68">
-        <v>266.99</v>
+        <v>262.88</v>
       </c>
       <c r="D68">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="E68">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="69">
@@ -1664,7 +1664,7 @@
         <v>64964</v>
       </c>
       <c r="C69">
-        <v>326.72</v>
+        <v>321.8</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -1683,13 +1683,13 @@
         <v>2174</v>
       </c>
       <c r="C70">
-        <v>192.35</v>
+        <v>190.35</v>
       </c>
       <c r="D70">
-        <v>22.73</v>
+        <v>23.03</v>
       </c>
       <c r="E70">
-        <v>22.73</v>
+        <v>23.03</v>
       </c>
     </row>
     <row r="71">
@@ -1702,13 +1702,13 @@
         <v>2353</v>
       </c>
       <c r="C71">
-        <v>118.48</v>
+        <v>117.27</v>
       </c>
       <c r="D71">
-        <v>28.21</v>
+        <v>28.83</v>
       </c>
       <c r="E71">
-        <v>28.21</v>
+        <v>28.83</v>
       </c>
     </row>
     <row r="72">
@@ -1721,13 +1721,13 @@
         <v>3743</v>
       </c>
       <c r="C72">
-        <v>319.51</v>
+        <v>315.28</v>
       </c>
       <c r="D72">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="E72">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="73">
@@ -1740,7 +1740,7 @@
         <v>82695</v>
       </c>
       <c r="C73">
-        <v>298.88</v>
+        <v>293.43</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         <v>30106</v>
       </c>
       <c r="C74">
-        <v>307.72</v>
+        <v>304.71</v>
       </c>
       <c r="D74">
         <v>0.01</v>
@@ -1778,7 +1778,7 @@
         <v>10634</v>
       </c>
       <c r="C75">
-        <v>298.92</v>
+        <v>293.66</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -1797,13 +1797,13 @@
         <v>114</v>
       </c>
       <c r="C76">
-        <v>166.38</v>
+        <v>164.24</v>
       </c>
       <c r="D76">
-        <v>31.33</v>
+        <v>31.9</v>
       </c>
       <c r="E76">
-        <v>31.72</v>
+        <v>32.29</v>
       </c>
     </row>
     <row r="77">
@@ -1816,13 +1816,13 @@
         <v>16578</v>
       </c>
       <c r="C77">
-        <v>205.38</v>
+        <v>202.81</v>
       </c>
       <c r="D77">
-        <v>22.19</v>
+        <v>22.41</v>
       </c>
       <c r="E77">
-        <v>22.19</v>
+        <v>22.41</v>
       </c>
     </row>
     <row r="78">
@@ -1835,13 +1835,13 @@
         <v>12430</v>
       </c>
       <c r="C78">
-        <v>252.56</v>
+        <v>249.84</v>
       </c>
       <c r="D78">
-        <v>13.43</v>
+        <v>13.66</v>
       </c>
       <c r="E78">
-        <v>15.28</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="79">
@@ -1854,13 +1854,13 @@
         <v>1885</v>
       </c>
       <c r="C79">
-        <v>123.5</v>
+        <v>122.28</v>
       </c>
       <c r="D79">
-        <v>22.48</v>
+        <v>22.96</v>
       </c>
       <c r="E79">
-        <v>41.45</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="80">
@@ -1873,13 +1873,13 @@
         <v>795</v>
       </c>
       <c r="C80">
-        <v>311.45</v>
+        <v>307.77</v>
       </c>
       <c r="D80">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="E80">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="81">
@@ -1892,13 +1892,13 @@
         <v>10780</v>
       </c>
       <c r="C81">
-        <v>219.53</v>
+        <v>216.96</v>
       </c>
       <c r="D81">
-        <v>11.12</v>
+        <v>11.27</v>
       </c>
       <c r="E81">
-        <v>13.42</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="82">
@@ -1911,13 +1911,13 @@
         <v>9629</v>
       </c>
       <c r="C82">
-        <v>221.81</v>
+        <v>219.23</v>
       </c>
       <c r="D82">
-        <v>19.54</v>
+        <v>19.7</v>
       </c>
       <c r="E82">
-        <v>19.54</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="83">
@@ -1930,13 +1930,13 @@
         <v>9679</v>
       </c>
       <c r="C83">
-        <v>185.45</v>
+        <v>182.97</v>
       </c>
       <c r="D83">
-        <v>23.99</v>
+        <v>24.87</v>
       </c>
       <c r="E83">
-        <v>23.99</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="84">
@@ -1949,7 +1949,7 @@
         <v>353</v>
       </c>
       <c r="C84">
-        <v>315.4</v>
+        <v>311.78</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -1968,13 +1968,13 @@
         <v>1358101</v>
       </c>
       <c r="C85">
-        <v>185.12</v>
+        <v>183.61</v>
       </c>
       <c r="D85">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="E85">
-        <v>5.12</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="86">
@@ -1987,13 +1987,13 @@
         <v>266686</v>
       </c>
       <c r="C86">
-        <v>308.82</v>
+        <v>306.23</v>
       </c>
       <c r="D86">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E86">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="87">
@@ -2006,13 +2006,13 @@
         <v>85202</v>
       </c>
       <c r="C87">
-        <v>226.46</v>
+        <v>224.54</v>
       </c>
       <c r="D87">
-        <v>7.31</v>
+        <v>7.51</v>
       </c>
       <c r="E87">
-        <v>10.5</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="88">
@@ -2025,13 +2025,13 @@
         <v>39650</v>
       </c>
       <c r="C88">
-        <v>254.35</v>
+        <v>251.89</v>
       </c>
       <c r="D88">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
       <c r="E88">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="89">
@@ -2044,13 +2044,13 @@
         <v>4843</v>
       </c>
       <c r="C89">
-        <v>258.77</v>
+        <v>255.71</v>
       </c>
       <c r="D89">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="E89">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="90">
@@ -2063,13 +2063,13 @@
         <v>8408</v>
       </c>
       <c r="C90">
-        <v>283.18</v>
+        <v>279.61</v>
       </c>
       <c r="D90">
-        <v>3.69</v>
+        <v>3.93</v>
       </c>
       <c r="E90">
-        <v>3.69</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="91">
@@ -2082,13 +2082,13 @@
         <v>59785</v>
       </c>
       <c r="C91">
-        <v>305.07</v>
+        <v>299.69</v>
       </c>
       <c r="D91">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="E91">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="92">
@@ -2101,13 +2101,13 @@
         <v>2788</v>
       </c>
       <c r="C92">
-        <v>311.85</v>
+        <v>308.91</v>
       </c>
       <c r="D92">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E92">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="93">
@@ -2120,13 +2120,13 @@
         <v>125913</v>
       </c>
       <c r="C93">
-        <v>213.77</v>
+        <v>209.02</v>
       </c>
       <c r="D93">
-        <v>0.95</v>
+        <v>1.48</v>
       </c>
       <c r="E93">
-        <v>0.95</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="94">
@@ -2139,13 +2139,13 @@
         <v>10346</v>
       </c>
       <c r="C94">
-        <v>265.59</v>
+        <v>263.39</v>
       </c>
       <c r="D94">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="E94">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="95">
@@ -2158,13 +2158,13 @@
         <v>18657</v>
       </c>
       <c r="C95">
-        <v>345.67</v>
+        <v>342.18</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="96">
@@ -2177,13 +2177,13 @@
         <v>49286</v>
       </c>
       <c r="C96">
-        <v>190.46</v>
+        <v>188.66</v>
       </c>
       <c r="D96">
-        <v>23.18</v>
+        <v>23.46</v>
       </c>
       <c r="E96">
-        <v>28.22</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="97">
@@ -2196,13 +2196,13 @@
         <v>120</v>
       </c>
       <c r="C97">
-        <v>262.73</v>
+        <v>259.9</v>
       </c>
       <c r="D97">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="E97">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="98">
@@ -2215,13 +2215,13 @@
         <v>4365</v>
       </c>
       <c r="C98">
-        <v>182.69</v>
+        <v>181.68</v>
       </c>
       <c r="D98">
-        <v>23.96</v>
+        <v>24.12</v>
       </c>
       <c r="E98">
-        <v>23.96</v>
+        <v>24.12</v>
       </c>
     </row>
     <row r="99">
@@ -2234,13 +2234,13 @@
         <v>6241</v>
       </c>
       <c r="C99">
-        <v>284.49</v>
+        <v>281.83</v>
       </c>
       <c r="D99">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="E99">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="100">
@@ -2253,13 +2253,13 @@
         <v>7020</v>
       </c>
       <c r="C100">
-        <v>480.9</v>
+        <v>476.78</v>
       </c>
       <c r="D100">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E100">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="101">
@@ -2272,13 +2272,13 @@
         <v>1901</v>
       </c>
       <c r="C101">
-        <v>249.62</v>
+        <v>245.66</v>
       </c>
       <c r="D101">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
       <c r="E101">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="102">
@@ -2291,7 +2291,7 @@
         <v>5797</v>
       </c>
       <c r="C102">
-        <v>414.89</v>
+        <v>410.8</v>
       </c>
       <c r="D102">
         <v>0.01</v>
@@ -2310,13 +2310,13 @@
         <v>2140</v>
       </c>
       <c r="C103">
-        <v>195.4</v>
+        <v>193.52</v>
       </c>
       <c r="D103">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="E103">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="104">
@@ -2329,13 +2329,13 @@
         <v>4838</v>
       </c>
       <c r="C104">
-        <v>226.74</v>
+        <v>224.48</v>
       </c>
       <c r="D104">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="E104">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="105">
@@ -2348,13 +2348,13 @@
         <v>6768</v>
       </c>
       <c r="C105">
-        <v>183.73</v>
+        <v>182.17</v>
       </c>
       <c r="D105">
-        <v>24.3</v>
+        <v>24.61</v>
       </c>
       <c r="E105">
-        <v>24.33</v>
+        <v>24.63</v>
       </c>
     </row>
     <row r="106">
@@ -2367,13 +2367,13 @@
         <v>2767</v>
       </c>
       <c r="C106">
-        <v>300.32</v>
+        <v>295.65</v>
       </c>
       <c r="D106">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="E106">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="107">
@@ -2386,7 +2386,7 @@
         <v>608</v>
       </c>
       <c r="C107">
-        <v>297.58</v>
+        <v>294.04</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -2405,13 +2405,13 @@
         <v>26962</v>
       </c>
       <c r="C108">
-        <v>97.76000000000001</v>
+        <v>96.83</v>
       </c>
       <c r="D108">
-        <v>57.26</v>
+        <v>58.81</v>
       </c>
       <c r="E108">
-        <v>65.43000000000001</v>
+        <v>67.08</v>
       </c>
     </row>
     <row r="109">
@@ -2424,13 +2424,13 @@
         <v>18176</v>
       </c>
       <c r="C109">
-        <v>316.34</v>
+        <v>313.09</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="110">
@@ -2443,13 +2443,13 @@
         <v>32675</v>
       </c>
       <c r="C110">
-        <v>228.26</v>
+        <v>226.37</v>
       </c>
       <c r="D110">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="E110">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="111">
@@ -2462,13 +2462,13 @@
         <v>474</v>
       </c>
       <c r="C111">
-        <v>315.93</v>
+        <v>313.77</v>
       </c>
       <c r="D111">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E111">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="112">
@@ -2481,7 +2481,7 @@
         <v>19932</v>
       </c>
       <c r="C112">
-        <v>306.57</v>
+        <v>302.99</v>
       </c>
       <c r="D112">
         <v>0.05</v>
@@ -2500,13 +2500,13 @@
         <v>489</v>
       </c>
       <c r="C113">
-        <v>288.15</v>
+        <v>284.53</v>
       </c>
       <c r="D113">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="E113">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="114">
@@ -2519,13 +2519,13 @@
         <v>44</v>
       </c>
       <c r="C114">
-        <v>289.16</v>
+        <v>286.75</v>
       </c>
       <c r="D114">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="E114">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="115">
@@ -2538,7 +2538,7 @@
         <v>4248</v>
       </c>
       <c r="C115">
-        <v>264.99</v>
+        <v>261.92</v>
       </c>
       <c r="D115">
         <v>0.02</v>
@@ -2557,13 +2557,13 @@
         <v>1275</v>
       </c>
       <c r="C116">
-        <v>250.3</v>
+        <v>248.21</v>
       </c>
       <c r="D116">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E116">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="117">
@@ -2576,13 +2576,13 @@
         <v>123071</v>
       </c>
       <c r="C117">
-        <v>266.03</v>
+        <v>262.87</v>
       </c>
       <c r="D117">
-        <v>5.74</v>
+        <v>5.92</v>
       </c>
       <c r="E117">
-        <v>5.74</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="118">
@@ -2595,13 +2595,13 @@
         <v>108</v>
       </c>
       <c r="C118">
-        <v>225.07</v>
+        <v>222.97</v>
       </c>
       <c r="D118">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="E118">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="119">
@@ -2614,13 +2614,13 @@
         <v>3094</v>
       </c>
       <c r="C119">
-        <v>129.08</v>
+        <v>127.69</v>
       </c>
       <c r="D119">
-        <v>25.51</v>
+        <v>26.71</v>
       </c>
       <c r="E119">
-        <v>25.51</v>
+        <v>26.71</v>
       </c>
     </row>
     <row r="120">
@@ -2633,13 +2633,13 @@
         <v>3126</v>
       </c>
       <c r="C120">
-        <v>338.78</v>
+        <v>335.49</v>
       </c>
       <c r="D120">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E120">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="121">
@@ -2652,7 +2652,7 @@
         <v>606</v>
       </c>
       <c r="C121">
-        <v>445.92</v>
+        <v>440.21</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -2671,13 +2671,13 @@
         <v>35374</v>
       </c>
       <c r="C122">
-        <v>296.33</v>
+        <v>293.96</v>
       </c>
       <c r="D122">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="E122">
-        <v>3.76</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="123">
@@ -2690,13 +2690,13 @@
         <v>28350</v>
       </c>
       <c r="C123">
-        <v>193.17</v>
+        <v>191.07</v>
       </c>
       <c r="D123">
-        <v>22.94</v>
+        <v>23.25</v>
       </c>
       <c r="E123">
-        <v>24.57</v>
+        <v>24.91</v>
       </c>
     </row>
     <row r="124">
@@ -2709,13 +2709,13 @@
         <v>51544</v>
       </c>
       <c r="C124">
-        <v>328.18</v>
+        <v>325.63</v>
       </c>
       <c r="D124">
-        <v>7.11</v>
+        <v>7.23</v>
       </c>
       <c r="E124">
-        <v>7.11</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="125">
@@ -2728,13 +2728,13 @@
         <v>2536</v>
       </c>
       <c r="C125">
-        <v>216.26</v>
+        <v>214.12</v>
       </c>
       <c r="D125">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="E125">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="126">
@@ -2747,13 +2747,13 @@
         <v>27554</v>
       </c>
       <c r="C126">
-        <v>240.25</v>
+        <v>238.09</v>
       </c>
       <c r="D126">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E126">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="127">
@@ -2766,13 +2766,13 @@
         <v>17302</v>
       </c>
       <c r="C127">
-        <v>305.39</v>
+        <v>301.16</v>
       </c>
       <c r="D127">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E127">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="128">
@@ -2785,13 +2785,13 @@
         <v>4883</v>
       </c>
       <c r="C128">
-        <v>325.21</v>
+        <v>321.07</v>
       </c>
       <c r="D128">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E128">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="129">
@@ -2804,13 +2804,13 @@
         <v>6308</v>
       </c>
       <c r="C129">
-        <v>239.97</v>
+        <v>237.09</v>
       </c>
       <c r="D129">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="E129">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="130">
@@ -2823,13 +2823,13 @@
         <v>21638</v>
       </c>
       <c r="C130">
-        <v>347.71</v>
+        <v>343.76</v>
       </c>
       <c r="D130">
         <v>0.01</v>
       </c>
       <c r="E130">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="131">
@@ -2842,13 +2842,13 @@
         <v>200330</v>
       </c>
       <c r="C131">
-        <v>201.2</v>
+        <v>199.11</v>
       </c>
       <c r="D131">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="E131">
-        <v>22.28</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="132">
@@ -2861,7 +2861,7 @@
         <v>1888</v>
       </c>
       <c r="C132">
-        <v>310.08</v>
+        <v>306.62</v>
       </c>
       <c r="D132">
         <v>0.01</v>
@@ -2880,13 +2880,13 @@
         <v>5273</v>
       </c>
       <c r="C133">
-        <v>322.88</v>
+        <v>318.65</v>
       </c>
       <c r="D133">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="E133">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="134">
@@ -2899,7 +2899,7 @@
         <v>4528</v>
       </c>
       <c r="C134">
-        <v>268.69</v>
+        <v>266.89</v>
       </c>
       <c r="D134">
         <v>0.04</v>
@@ -2918,13 +2918,13 @@
         <v>222488</v>
       </c>
       <c r="C135">
-        <v>171.82</v>
+        <v>170.05</v>
       </c>
       <c r="D135">
-        <v>3.73</v>
+        <v>4.01</v>
       </c>
       <c r="E135">
-        <v>7.92</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="136">
@@ -2937,7 +2937,7 @@
         <v>4759</v>
       </c>
       <c r="C136">
-        <v>915.13</v>
+        <v>905.08</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -2956,13 +2956,13 @@
         <v>4126</v>
       </c>
       <c r="C137">
-        <v>277</v>
+        <v>273.45</v>
       </c>
       <c r="D137">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="E137">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="138">
@@ -2975,13 +2975,13 @@
         <v>9256</v>
       </c>
       <c r="C138">
-        <v>218.42</v>
+        <v>216.37</v>
       </c>
       <c r="D138">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="E138">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="139">
@@ -2994,13 +2994,13 @@
         <v>6333</v>
       </c>
       <c r="C139">
-        <v>306.53</v>
+        <v>302.65</v>
       </c>
       <c r="D139">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="E139">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="140">
@@ -3013,13 +3013,13 @@
         <v>31699</v>
       </c>
       <c r="C140">
-        <v>286.8</v>
+        <v>283.21</v>
       </c>
       <c r="D140">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="E140">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="141">
@@ -3032,13 +3032,13 @@
         <v>107874</v>
       </c>
       <c r="C141">
-        <v>321.37</v>
+        <v>318.76</v>
       </c>
       <c r="D141">
-        <v>7.53</v>
+        <v>7.64</v>
       </c>
       <c r="E141">
-        <v>7.53</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="142">
@@ -3051,13 +3051,13 @@
         <v>37855</v>
       </c>
       <c r="C142">
-        <v>273.91</v>
+        <v>270.78</v>
       </c>
       <c r="D142">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="E142">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="143">
@@ -3070,13 +3070,13 @@
         <v>10237</v>
       </c>
       <c r="C143">
-        <v>309.65</v>
+        <v>304.51</v>
       </c>
       <c r="D143">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="E143">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="144">
@@ -3089,7 +3089,7 @@
         <v>2752</v>
       </c>
       <c r="C144">
-        <v>262.96</v>
+        <v>262.02</v>
       </c>
       <c r="D144">
         <v>0.05</v>
@@ -3108,13 +3108,13 @@
         <v>19349</v>
       </c>
       <c r="C145">
-        <v>285.94</v>
+        <v>282.15</v>
       </c>
       <c r="D145">
-        <v>0.41</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E145">
-        <v>0.41</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -3127,13 +3127,13 @@
         <v>144900</v>
       </c>
       <c r="C146">
-        <v>259.17</v>
+        <v>256.1</v>
       </c>
       <c r="D146">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="E146">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="147">
@@ -3146,13 +3146,13 @@
         <v>12256</v>
       </c>
       <c r="C147">
-        <v>264.41</v>
+        <v>261.89</v>
       </c>
       <c r="D147">
-        <v>11.37</v>
+        <v>11.54</v>
       </c>
       <c r="E147">
-        <v>15.31</v>
+        <v>15.53</v>
       </c>
     </row>
     <row r="148">
@@ -3165,13 +3165,13 @@
         <v>203</v>
       </c>
       <c r="C148">
-        <v>304.34</v>
+        <v>300.53</v>
       </c>
       <c r="D148">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E148">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="149">
@@ -3184,7 +3184,7 @@
         <v>29560</v>
       </c>
       <c r="C149">
-        <v>351.37</v>
+        <v>349.05</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -3203,13 +3203,13 @@
         <v>15639</v>
       </c>
       <c r="C150">
-        <v>229.74</v>
+        <v>227.41</v>
       </c>
       <c r="D150">
-        <v>16.27</v>
+        <v>16.52</v>
       </c>
       <c r="E150">
-        <v>17.32</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="151">
@@ -3222,13 +3222,13 @@
         <v>6928</v>
       </c>
       <c r="C151">
-        <v>344.36</v>
+        <v>339.49</v>
       </c>
       <c r="D151">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="E151">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="152">
@@ -3241,13 +3241,13 @@
         <v>115</v>
       </c>
       <c r="C152">
-        <v>193.73</v>
+        <v>192</v>
       </c>
       <c r="D152">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="E152">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="153">
@@ -3260,7 +3260,7 @@
         <v>7405</v>
       </c>
       <c r="C153">
-        <v>301.93</v>
+        <v>299.03</v>
       </c>
       <c r="D153">
         <v>0.01</v>
@@ -3279,13 +3279,13 @@
         <v>5611</v>
       </c>
       <c r="C154">
-        <v>290.16</v>
+        <v>287.89</v>
       </c>
       <c r="D154">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="E154">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="155">
@@ -3298,13 +3298,13 @@
         <v>5388</v>
       </c>
       <c r="C155">
-        <v>174.56</v>
+        <v>172.65</v>
       </c>
       <c r="D155">
-        <v>4.39</v>
+        <v>5.72</v>
       </c>
       <c r="E155">
-        <v>4.39</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="156">
@@ -3317,13 +3317,13 @@
         <v>2057</v>
       </c>
       <c r="C156">
-        <v>224.19</v>
+        <v>220.87</v>
       </c>
       <c r="D156">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
       <c r="E156">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="157">
@@ -3336,13 +3336,13 @@
         <v>700</v>
       </c>
       <c r="C157">
-        <v>297.22</v>
+        <v>293.9</v>
       </c>
       <c r="D157">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="E157">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="158">
@@ -3355,7 +3355,7 @@
         <v>57950</v>
       </c>
       <c r="C158">
-        <v>295.21</v>
+        <v>292.52</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -3374,13 +3374,13 @@
         <v>51388</v>
       </c>
       <c r="C159">
-        <v>260.26</v>
+        <v>257.34</v>
       </c>
       <c r="D159">
-        <v>4.94</v>
+        <v>5.32</v>
       </c>
       <c r="E159">
-        <v>5.47</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="160">
@@ -3393,13 +3393,13 @@
         <v>10007</v>
       </c>
       <c r="C160">
-        <v>243.73</v>
+        <v>241.46</v>
       </c>
       <c r="D160">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="E160">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="161">
@@ -3412,13 +3412,13 @@
         <v>46862</v>
       </c>
       <c r="C161">
-        <v>269.02</v>
+        <v>264.92</v>
       </c>
       <c r="D161">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="E161">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="162">
@@ -3431,13 +3431,13 @@
         <v>21998</v>
       </c>
       <c r="C162">
-        <v>221.47</v>
+        <v>219.39</v>
       </c>
       <c r="D162">
-        <v>16.99</v>
+        <v>17.33</v>
       </c>
       <c r="E162">
-        <v>20.45</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="163">
@@ -3450,13 +3450,13 @@
         <v>175</v>
       </c>
       <c r="C163">
-        <v>130.76</v>
+        <v>129.43</v>
       </c>
       <c r="D163">
-        <v>26.89</v>
+        <v>27.77</v>
       </c>
       <c r="E163">
-        <v>26.89</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="164">
@@ -3469,13 +3469,13 @@
         <v>103</v>
       </c>
       <c r="C164">
-        <v>270.63</v>
+        <v>267.07</v>
       </c>
       <c r="D164">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E164">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="165">
@@ -3488,7 +3488,7 @@
         <v>43422</v>
       </c>
       <c r="C165">
-        <v>267.6</v>
+        <v>264.88</v>
       </c>
       <c r="D165">
         <v>0.04</v>
@@ -3507,13 +3507,13 @@
         <v>592</v>
       </c>
       <c r="C166">
-        <v>228.83</v>
+        <v>226.11</v>
       </c>
       <c r="D166">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="E166">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="167">
@@ -3526,13 +3526,13 @@
         <v>10114</v>
       </c>
       <c r="C167">
-        <v>232.89</v>
+        <v>229.21</v>
       </c>
       <c r="D167">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="E167">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="168">
@@ -3545,13 +3545,13 @@
         <v>8460</v>
       </c>
       <c r="C168">
-        <v>209.32</v>
+        <v>206.26</v>
       </c>
       <c r="D168">
-        <v>0.45</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E168">
-        <v>0.45</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -3564,13 +3564,13 @@
         <v>19584</v>
       </c>
       <c r="C169">
-        <v>221.36</v>
+        <v>219.66</v>
       </c>
       <c r="D169">
-        <v>8.449999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E169">
-        <v>8.640000000000001</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="170">
@@ -3583,13 +3583,13 @@
         <v>206</v>
       </c>
       <c r="C170">
-        <v>192.45</v>
+        <v>190.39</v>
       </c>
       <c r="D170">
-        <v>22.66</v>
+        <v>22.99</v>
       </c>
       <c r="E170">
-        <v>22.81</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="171">
@@ -3602,13 +3602,13 @@
         <v>23498</v>
       </c>
       <c r="C171">
-        <v>259.62</v>
+        <v>256.77</v>
       </c>
       <c r="D171">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="E171">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="172">
@@ -3621,13 +3621,13 @@
         <v>9151</v>
       </c>
       <c r="C172">
-        <v>294.1</v>
+        <v>291.2</v>
       </c>
       <c r="D172">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="E172">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="173">
@@ -3640,13 +3640,13 @@
         <v>56218</v>
       </c>
       <c r="C173">
-        <v>186.9</v>
+        <v>184.88</v>
       </c>
       <c r="D173">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="E173">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="174">
@@ -3659,13 +3659,13 @@
         <v>70794</v>
       </c>
       <c r="C174">
-        <v>152.33</v>
+        <v>150.88</v>
       </c>
       <c r="D174">
-        <v>7.35</v>
+        <v>8.48</v>
       </c>
       <c r="E174">
-        <v>8.199999999999999</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="175">
@@ -3678,7 +3678,7 @@
         <v>1255</v>
       </c>
       <c r="C175">
-        <v>384.76</v>
+        <v>381.15</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>8095</v>
       </c>
       <c r="C176">
-        <v>266.48</v>
+        <v>263.84</v>
       </c>
       <c r="D176">
         <v>0.18</v>
@@ -3716,13 +3716,13 @@
         <v>103</v>
       </c>
       <c r="C177">
-        <v>223.09</v>
+        <v>220.31</v>
       </c>
       <c r="D177">
-        <v>9.619999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E177">
-        <v>11.29</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="178">
@@ -3735,13 +3735,13 @@
         <v>1474</v>
       </c>
       <c r="C178">
-        <v>107.58</v>
+        <v>106.52</v>
       </c>
       <c r="D178">
-        <v>53.97</v>
+        <v>54.43</v>
       </c>
       <c r="E178">
-        <v>53.97</v>
+        <v>54.43</v>
       </c>
     </row>
     <row r="179">
@@ -3754,13 +3754,13 @@
         <v>11620</v>
       </c>
       <c r="C179">
-        <v>298.26</v>
+        <v>295.52</v>
       </c>
       <c r="D179">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E179">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -3773,13 +3773,13 @@
         <v>83603</v>
       </c>
       <c r="C180">
-        <v>264.11</v>
+        <v>261.7</v>
       </c>
       <c r="D180">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="E180">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="181">
@@ -3792,13 +3792,13 @@
         <v>6563</v>
       </c>
       <c r="C181">
-        <v>263.67</v>
+        <v>261.25</v>
       </c>
       <c r="D181">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="E181">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="182">
@@ -3811,13 +3811,13 @@
         <v>40741</v>
       </c>
       <c r="C182">
-        <v>225.96</v>
+        <v>223.57</v>
       </c>
       <c r="D182">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="E182">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="183">
@@ -3830,13 +3830,13 @@
         <v>44714</v>
       </c>
       <c r="C183">
-        <v>186.44</v>
+        <v>184.08</v>
       </c>
       <c r="D183">
-        <v>1.91</v>
+        <v>2.77</v>
       </c>
       <c r="E183">
-        <v>1.91</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="184">
@@ -3849,13 +3849,13 @@
         <v>9297</v>
       </c>
       <c r="C184">
-        <v>226.74</v>
+        <v>225.85</v>
       </c>
       <c r="D184">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="E184">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="185">
@@ -3868,13 +3868,13 @@
         <v>66201</v>
       </c>
       <c r="C185">
-        <v>220.53</v>
+        <v>217.24</v>
       </c>
       <c r="D185">
-        <v>0.79</v>
+        <v>1.11</v>
       </c>
       <c r="E185">
-        <v>0.79</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="186">
@@ -3887,13 +3887,13 @@
         <v>332631</v>
       </c>
       <c r="C186">
-        <v>256.1</v>
+        <v>252.91</v>
       </c>
       <c r="D186">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="E186">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="187">
@@ -3906,13 +3906,13 @@
         <v>3357</v>
       </c>
       <c r="C187">
-        <v>316.94</v>
+        <v>311.89</v>
       </c>
       <c r="D187">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="E187">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="188">
@@ -3925,13 +3925,13 @@
         <v>31893</v>
       </c>
       <c r="C188">
-        <v>350.82</v>
+        <v>347.54</v>
       </c>
       <c r="D188">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="E188">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="189">
@@ -3944,13 +3944,13 @@
         <v>280</v>
       </c>
       <c r="C189">
-        <v>357.08</v>
+        <v>352.92</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="190">
@@ -3963,13 +3963,13 @@
         <v>28801</v>
       </c>
       <c r="C190">
-        <v>206.94</v>
+        <v>204.44</v>
       </c>
       <c r="D190">
-        <v>3.39</v>
+        <v>3.63</v>
       </c>
       <c r="E190">
-        <v>3.39</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="191">
@@ -3982,13 +3982,13 @@
         <v>95272</v>
       </c>
       <c r="C191">
-        <v>330.46</v>
+        <v>327.61</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="192">
@@ -4001,13 +4001,13 @@
         <v>33392</v>
       </c>
       <c r="C192">
-        <v>274.99</v>
+        <v>272.37</v>
       </c>
       <c r="D192">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="E192">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="193">
@@ -4020,7 +4020,7 @@
         <v>17625</v>
       </c>
       <c r="C193">
-        <v>236.9</v>
+        <v>234.55</v>
       </c>
       <c r="D193">
         <v>0.32</v>
@@ -4039,13 +4039,13 @@
         <v>14694</v>
       </c>
       <c r="C194">
-        <v>187.14</v>
+        <v>185.23</v>
       </c>
       <c r="D194">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="E194">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>
